--- a/public/contoh_excel/TEMPLATE BUAT TAGIHAN.xlsx
+++ b/public/contoh_excel/TEMPLATE BUAT TAGIHAN.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Tagihan" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,43 +15,106 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
-  <si>
-    <t>NIS</t>
-  </si>
-  <si>
-    <t>NOMINAL</t>
-  </si>
-  <si>
-    <t>NAMA_TAGIHAN</t>
-  </si>
-  <si>
-    <t>PERIODE</t>
-  </si>
-  <si>
-    <t>TAHUN_AKADEMIK</t>
-  </si>
-  <si>
-    <t>CICIL</t>
-  </si>
-  <si>
-    <t>1234567801</t>
-  </si>
-  <si>
-    <t>BULAN SEPTEMBER</t>
-  </si>
-  <si>
-    <t>202609</t>
-  </si>
-  <si>
-    <t>2026/2027</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+  <si>
+    <t>Nomor Tagihan</t>
+  </si>
+  <si>
+    <t>Nomor Pembayaran</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Tanggal Aktif</t>
+  </si>
+  <si>
+    <t>Tanggal Berakhir</t>
+  </si>
+  <si>
+    <t>Urutan</t>
+  </si>
+  <si>
+    <t>Jenis Tagihan</t>
+  </si>
+  <si>
+    <t>Atribut 1</t>
+  </si>
+  <si>
+    <t>Atribut 2</t>
+  </si>
+  <si>
+    <t>Atribut 3</t>
+  </si>
+  <si>
+    <t>Total Nominal</t>
+  </si>
+  <si>
+    <t>Rincian 1</t>
+  </si>
+  <si>
+    <t>Nominal 1</t>
+  </si>
+  <si>
+    <t>Rincian 2</t>
+  </si>
+  <si>
+    <t>Nominal 2</t>
+  </si>
+  <si>
+    <t>20100003-001</t>
+  </si>
+  <si>
+    <t>9007888500252</t>
+  </si>
+  <si>
+    <t>CONTOH SISWA GEMA NURANI</t>
+  </si>
+  <si>
+    <t>contoh@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-10-31 23:59:59</t>
+  </si>
+  <si>
+    <t>KELAS 2</t>
+  </si>
+  <si>
+    <t>SDIT GEMA NURANI</t>
+  </si>
+  <si>
+    <t>TAHUN AJARAN 2026-2027</t>
+  </si>
+  <si>
+    <t>SPP</t>
+  </si>
+  <si>
+    <t>20100003-002</t>
+  </si>
+  <si>
+    <t>9007888500177</t>
+  </si>
+  <si>
+    <t>CONTOH SISWA DUA</t>
+  </si>
+  <si>
+    <t>contoh2@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <b val="0"/>
@@ -68,19 +131,25 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF305496"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,13 +157,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="165" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="3" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,22 +489,32 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="5"/>
+    <col min="2" max="2" width="22.28" bestFit="true" customWidth="true" style="5"/>
+    <col min="3" max="3" width="29.421" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.426" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="13.997" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" customHeight="1" ht="22">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -424,26 +529,128 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>300000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2">
+    <row r="2" spans="1:16">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2">
         <v>1</v>
       </c>
+      <c r="H2" s="2">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="8">
+        <v>500000</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="8">
+        <v>500000</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8">
+        <v>500000</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="8">
+        <v>500000</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="8"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
